--- a/data/trans_orig/IP06-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP06-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8947</t>
+          <t>9178</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20668</t>
+          <t>20921</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12829</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25936</t>
+          <t>26301</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24828</t>
+          <t>24920</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>42966</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>7687</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34519</t>
+          <t>36085</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54203</t>
+          <t>53919</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34960</t>
+          <t>34776</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53311</t>
+          <t>52257</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>73720</t>
+          <t>74234</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>100003</t>
+          <t>100056</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71814</t>
+          <t>70309</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91523</t>
+          <t>90366</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77671</t>
+          <t>76986</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96530</t>
+          <t>96159</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>152666</t>
+          <t>154364</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>180777</t>
+          <t>181079</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,06%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16520</t>
+          <t>16597</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30918</t>
+          <t>29901</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20354</t>
+          <t>20659</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>28876</t>
+          <t>29047</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>46740</t>
+          <t>47051</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11300</t>
+          <t>10687</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14281</t>
+          <t>14995</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47203</t>
+          <t>47241</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66408</t>
+          <t>66654</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50051</t>
+          <t>50279</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70468</t>
+          <t>71230</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103300</t>
+          <t>103483</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132675</t>
+          <t>133227</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100075</t>
+          <t>102161</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>121857</t>
+          <t>121983</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>120236</t>
+          <t>120623</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>142461</t>
+          <t>142962</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>228133</t>
+          <t>226256</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>258906</t>
+          <t>257715</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9185</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20157</t>
+          <t>19752</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,39 +1885,39 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>14,4%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>10031</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5813</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>15491</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>6,7%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14,69%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>10031</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>5809</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>15260</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>6,7%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>3,88%</t>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17830</t>
+          <t>17352</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32452</t>
+          <t>31160</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10610</t>
+          <t>10019</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33237</t>
+          <t>33161</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49574</t>
+          <t>49836</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39079</t>
+          <t>38962</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56789</t>
+          <t>57304</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77497</t>
+          <t>76676</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103318</t>
+          <t>101260</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70423</t>
+          <t>69628</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87973</t>
+          <t>88070</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>80154</t>
+          <t>79688</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>99287</t>
+          <t>98691</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>155165</t>
+          <t>156173</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>181641</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,32%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19922</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35954</t>
+          <t>36657</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16251</t>
+          <t>15948</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30690</t>
+          <t>31331</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39539</t>
+          <t>39580</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62596</t>
+          <t>61505</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>699</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>6649</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9476</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41618</t>
+          <t>41821</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>62978</t>
+          <t>63319</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43485</t>
+          <t>42866</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64603</t>
+          <t>63431</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>92745</t>
+          <t>90843</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>121899</t>
+          <t>120324</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,94%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>116663</t>
+          <t>116106</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140332</t>
+          <t>140149</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>117152</t>
+          <t>116021</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138813</t>
+          <t>139763</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>240538</t>
+          <t>240116</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>272386</t>
+          <t>273362</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,75%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>65212</t>
+          <t>64989</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>92110</t>
+          <t>91919</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>54020</t>
+          <t>54844</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>78123</t>
+          <t>80245</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>126939</t>
+          <t>127448</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>162040</t>
+          <t>163766</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13261</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21978</t>
+          <t>23318</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16916</t>
+          <t>16487</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32073</t>
+          <t>31098</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>174733</t>
+          <t>175235</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>212872</t>
+          <t>214808</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>185003</t>
+          <t>184921</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>222777</t>
+          <t>223767</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>373172</t>
+          <t>372173</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>424209</t>
+          <t>426882</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>378413</t>
+          <t>376609</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>419881</t>
+          <t>419789</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>415162</t>
+          <t>414848</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>457041</t>
+          <t>456953</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>807728</t>
+          <t>804653</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>864873</t>
+          <t>865819</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,8%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11945</t>
+          <t>12776</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13142</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>8909</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21615</t>
+          <t>21926</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9394</t>
+          <t>10135</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33704</t>
+          <t>33647</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52364</t>
+          <t>51736</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41647</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60851</t>
+          <t>62020</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78283</t>
+          <t>78363</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>106345</t>
+          <t>107132</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79419</t>
+          <t>78482</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>98188</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>81866</t>
+          <t>81965</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102798</t>
+          <t>101635</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>168389</t>
+          <t>166304</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>197798</t>
+          <t>195734</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,71%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19933</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>8555</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20448</t>
+          <t>20645</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19514</t>
+          <t>20262</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>35950</t>
+          <t>36918</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2669</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>10466</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>9923</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6745</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17043</t>
+          <t>17509</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51422</t>
+          <t>51805</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72135</t>
+          <t>72160</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61527</t>
+          <t>61561</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83857</t>
+          <t>84244</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>118732</t>
+          <t>117635</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>151003</t>
+          <t>148973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>34,63%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>113332</t>
+          <t>114430</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>135297</t>
+          <t>137216</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>121055</t>
+          <t>121412</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>143684</t>
+          <t>144155</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>240495</t>
+          <t>242272</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>274246</t>
+          <t>274920</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,91%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17849</t>
+          <t>16529</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10279</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23936</t>
+          <t>24058</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19606</t>
+          <t>20455</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36906</t>
+          <t>38276</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>429</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7019</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2242</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33057</t>
+          <t>34084</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51274</t>
+          <t>51415</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45089</t>
+          <t>44234</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64665</t>
+          <t>62978</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82796</t>
+          <t>82357</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107854</t>
+          <t>107938</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,52%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90360</t>
+          <t>92102</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>110112</t>
+          <t>110381</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81654</t>
+          <t>83058</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103011</t>
+          <t>103418</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>180525</t>
+          <t>180076</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>208136</t>
+          <t>208510</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,76%</t>
         </is>
       </c>
     </row>
@@ -5516,12 +5516,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15305</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31332</t>
+          <t>30728</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5551,12 +5551,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17988</t>
+          <t>17456</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33703</t>
+          <t>33911</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37597</t>
+          <t>37444</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59890</t>
+          <t>60705</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8509</t>
+          <t>8802</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>712</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>13027</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -5742,12 +5742,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43924</t>
+          <t>44151</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>65026</t>
+          <t>66691</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5777,12 +5777,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54690</t>
+          <t>54067</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>76446</t>
+          <t>75666</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>104143</t>
+          <t>102766</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>134756</t>
+          <t>133586</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>115277</t>
+          <t>115034</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140224</t>
+          <t>140748</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>103122</t>
+          <t>104517</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>127067</t>
+          <t>128391</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>225991</t>
+          <t>228109</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>261806</t>
+          <t>261445</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,67%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>44177</t>
+          <t>44080</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67485</t>
+          <t>68015</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>51021</t>
+          <t>51175</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>78783</t>
+          <t>77619</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>99098</t>
+          <t>101921</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>134250</t>
+          <t>137613</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>19222</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23599</t>
+          <t>22707</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20589</t>
+          <t>20610</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37227</t>
+          <t>37372</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>178892</t>
+          <t>179692</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>218806</t>
+          <t>218660</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>219488</t>
+          <t>220119</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>262649</t>
+          <t>263456</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>411370</t>
+          <t>412275</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>467524</t>
+          <t>470297</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -6424,12 +6424,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>423095</t>
+          <t>422645</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>465248</t>
+          <t>464125</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>409879</t>
+          <t>410542</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>454816</t>
+          <t>455587</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>846905</t>
+          <t>846657</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>908413</t>
+          <t>909090</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,15%</t>
         </is>
       </c>
     </row>
@@ -6886,12 +6886,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12665</t>
+          <t>12537</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15909</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9682</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23063</t>
+          <t>23594</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -6999,12 +6999,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14401</t>
+          <t>14261</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18588</t>
+          <t>20093</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -7112,12 +7112,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20808</t>
+          <t>20895</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36519</t>
+          <t>36929</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33762</t>
+          <t>33800</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53170</t>
+          <t>53323</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>58920</t>
+          <t>59208</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>85147</t>
+          <t>82346</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80183</t>
+          <t>78574</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98323</t>
+          <t>97151</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>81875</t>
+          <t>82935</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102790</t>
+          <t>103448</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>168198</t>
+          <t>169732</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>195654</t>
+          <t>196046</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,74%</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7455,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11147</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23348</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>13040</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27877</t>
+          <t>27398</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>27847</t>
+          <t>27795</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>47743</t>
+          <t>47413</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -7568,12 +7568,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>6979</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7583,12 +7583,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>8295</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12738</t>
+          <t>12329</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -7681,12 +7681,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39992</t>
+          <t>39582</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59092</t>
+          <t>58407</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7696,12 +7696,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35799</t>
+          <t>36043</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56096</t>
+          <t>55064</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81955</t>
+          <t>79476</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>107493</t>
+          <t>106893</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126965</t>
+          <t>127912</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>147686</t>
+          <t>148350</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>144597</t>
+          <t>146134</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>167666</t>
+          <t>166209</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>278458</t>
+          <t>279892</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>309414</t>
+          <t>309643</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,74%</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7299</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17640</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8039,12 +8039,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10547</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23537</t>
+          <t>23458</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20254</t>
+          <t>20256</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36403</t>
+          <t>37950</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31593</t>
+          <t>31496</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48509</t>
+          <t>48748</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8265,12 +8265,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31039</t>
+          <t>30978</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50241</t>
+          <t>49276</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67239</t>
+          <t>67687</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>92248</t>
+          <t>91682</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8363,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94602</t>
+          <t>94584</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112096</t>
+          <t>112253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98624</t>
+          <t>98730</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>119317</t>
+          <t>119561</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>198787</t>
+          <t>198972</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>226101</t>
+          <t>225662</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,08%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13275</t>
+          <t>13256</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28424</t>
+          <t>27352</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12882</t>
+          <t>12928</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26170</t>
+          <t>25971</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29278</t>
+          <t>29391</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48731</t>
+          <t>48535</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8216</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>575</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10745</t>
+          <t>10766</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -8819,12 +8819,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36112</t>
+          <t>36175</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56167</t>
+          <t>55740</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30801</t>
+          <t>30886</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49210</t>
+          <t>49133</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8889,12 +8889,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73932</t>
+          <t>73215</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>100577</t>
+          <t>101138</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -8932,12 +8932,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>123537</t>
+          <t>124916</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>146682</t>
+          <t>146699</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>134485</t>
+          <t>134535</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>155684</t>
+          <t>155955</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>264134</t>
+          <t>264044</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>294149</t>
+          <t>295050</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,97%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>44459</t>
+          <t>45443</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67429</t>
+          <t>69407</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49890</t>
+          <t>50467</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>75597</t>
+          <t>76897</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>100410</t>
+          <t>102634</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>134263</t>
+          <t>135872</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -9275,12 +9275,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23984</t>
+          <t>24300</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>17172</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9345,12 +9345,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18565</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35622</t>
+          <t>36353</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -9388,12 +9388,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>143340</t>
+          <t>145741</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>181036</t>
+          <t>181763</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>149857</t>
+          <t>149442</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>187645</t>
+          <t>185994</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>304455</t>
+          <t>304775</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>357538</t>
+          <t>356708</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9473,12 +9473,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>447027</t>
+          <t>444353</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>487702</t>
+          <t>485727</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>479772</t>
+          <t>483533</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>524566</t>
+          <t>524644</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>939566</t>
+          <t>940932</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>998594</t>
+          <t>999045</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9586,12 +9586,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,15%</t>
         </is>
       </c>
     </row>
